--- a/data/trans_orig/P79A7_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P79A7_2023-Estudios-trans_orig.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1163</t>
+          <t>1319</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>1163</t>
+          <t>1319</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1163</t>
+          <t>1319</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1163</t>
+          <t>1319</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1163</t>
+          <t>1319</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1163</t>
+          <t>1319</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1163</t>
+          <t>1319</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1163</t>
+          <t>1319</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,27 +1068,27 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5022</t>
+          <t>5642</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1544</t>
+          <t>1915</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8347</t>
+          <t>8721</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>60,17%</t>
+          <t>64,7%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4840</t>
+          <t>5271</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -1138,27 +1138,27 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>9862</t>
+          <t>10913</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5279</t>
+          <t>5533</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13187</t>
+          <t>13992</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>74,79%</t>
+          <t>78,0%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>40,03%</t>
+          <t>39,54%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>3325</t>
+          <t>3079</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1191,12 +1191,12 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6807</t>
+          <t>6803</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>39,83%</t>
+          <t>35,3%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>81,54%</t>
+          <t>78,0%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1251,7 +1251,7 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>3325</t>
+          <t>3079</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
@@ -1261,12 +1261,12 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>7908</t>
+          <t>8459</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>59,97%</t>
+          <t>60,46%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8347</t>
+          <t>8721</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8347</t>
+          <t>8721</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8347</t>
+          <t>8721</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4840</t>
+          <t>5271</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4840</t>
+          <t>5271</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4840</t>
+          <t>5271</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>13187</t>
+          <t>13992</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>13187</t>
+          <t>13992</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>13187</t>
+          <t>13992</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>4026</t>
+          <t>4505</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>740</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>4696</t>
+          <t>5244</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4026</t>
+          <t>4505</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4026</t>
+          <t>4505</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4026</t>
+          <t>4505</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>740</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>740</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>740</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>4696</t>
+          <t>5244</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>4696</t>
+          <t>5244</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>4696</t>
+          <t>5244</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,27 +1754,27 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9047</t>
+          <t>10147</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4005</t>
+          <t>5963</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12372</t>
+          <t>13226</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>73,13%</t>
+          <t>76,72%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>45,09%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6673</t>
+          <t>7330</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1824,27 +1824,27 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>15721</t>
+          <t>17477</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10286</t>
+          <t>11459</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>19046</t>
+          <t>20556</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>82,54%</t>
+          <t>85,02%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>54,01%</t>
+          <t>55,75%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1867,7 +1867,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3325</t>
+          <t>3079</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1877,12 +1877,12 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8367</t>
+          <t>7263</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1892,7 +1892,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>67,63%</t>
+          <t>54,91%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>3325</t>
+          <t>3079</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
@@ -1947,12 +1947,12 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>8760</t>
+          <t>9097</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>45,99%</t>
+          <t>44,25%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>12372</t>
+          <t>13226</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>12372</t>
+          <t>13226</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>12372</t>
+          <t>13226</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6673</t>
+          <t>7330</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6673</t>
+          <t>7330</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6673</t>
+          <t>7330</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>19046</t>
+          <t>20556</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>19046</t>
+          <t>20556</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>19046</t>
+          <t>20556</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
